--- a/artfynd/A 10060-2022 artfynd.xlsx
+++ b/artfynd/A 10060-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10060-2022 artfynd.xlsx
+++ b/artfynd/A 10060-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70700986</v>
+        <v>104432856</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>S om Tjulån  o Sputn, Ly lm</t>
+          <t>Tjulån södra, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553352.9378608643</v>
+        <v>553329</v>
       </c>
       <c r="R2" t="n">
-        <v>7314455.863492748</v>
+        <v>7314364</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,46 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maja Agnemo</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maja Agnemo</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104432855</v>
+        <v>104432873</v>
       </c>
       <c r="B3" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553319.8191519352</v>
+        <v>553290</v>
       </c>
       <c r="R3" t="n">
-        <v>7314347.478741837</v>
+        <v>7314345</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -877,19 +840,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104432853</v>
+        <v>104432872</v>
       </c>
       <c r="B4" t="n">
-        <v>89317</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3242</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -956,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553294.3320100137</v>
+        <v>553328</v>
       </c>
       <c r="R4" t="n">
-        <v>7314399.253076466</v>
+        <v>7314384</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -989,19 +937,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104432871</v>
+        <v>104432865</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1068,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553388.3598101781</v>
+        <v>553215</v>
       </c>
       <c r="R5" t="n">
-        <v>7314397.337099082</v>
+        <v>7314647</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1101,19 +1034,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104432865</v>
+        <v>104796701</v>
       </c>
       <c r="B6" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1467</v>
+        <v>1503</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1180,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553214.9228788411</v>
+        <v>553414</v>
       </c>
       <c r="R6" t="n">
-        <v>7314647.172137323</v>
+        <v>7315164</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1213,19 +1131,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104432872</v>
+        <v>104433019</v>
       </c>
       <c r="B7" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1292,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553328.5440630831</v>
+        <v>553230</v>
       </c>
       <c r="R7" t="n">
-        <v>7314383.564131063</v>
+        <v>7314704</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1325,19 +1228,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104432856</v>
+        <v>104432853</v>
       </c>
       <c r="B8" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>3242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1404,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553328.9177818322</v>
+        <v>553294</v>
       </c>
       <c r="R8" t="n">
-        <v>7314363.568963841</v>
+        <v>7314399</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1437,19 +1325,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104432873</v>
+        <v>104432876</v>
       </c>
       <c r="B9" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>4217</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1516,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553290.0272902441</v>
+        <v>553218</v>
       </c>
       <c r="R9" t="n">
-        <v>7314345.289329655</v>
+        <v>7314705</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1549,19 +1422,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104432864</v>
+        <v>104432857</v>
       </c>
       <c r="B10" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1628,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553378.4952489688</v>
+        <v>553216</v>
       </c>
       <c r="R10" t="n">
-        <v>7315230.175877432</v>
+        <v>7314715</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1661,24 +1519,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,53 +1548,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104432870</v>
+        <v>70700986</v>
       </c>
       <c r="B11" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tjulån södra, Ly lm</t>
+          <t>S om Tjulån  o Sputn, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553371.8392492867</v>
+        <v>553353</v>
       </c>
       <c r="R11" t="n">
-        <v>7314341.103514467</v>
+        <v>7314456</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1775,22 +1615,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,53 +1631,63 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Maja Agnemo</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Maja Agnemo</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104432867</v>
+        <v>104432871</v>
       </c>
       <c r="B12" t="n">
-        <v>77532</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1857,10 +1697,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553422.8586757048</v>
+        <v>553388</v>
       </c>
       <c r="R12" t="n">
-        <v>7315195.502814186</v>
+        <v>7314397</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1890,19 +1730,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,37 +1759,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104432860</v>
+        <v>104432867</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1969,10 +1794,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553206.7141355241</v>
+        <v>553423</v>
       </c>
       <c r="R13" t="n">
-        <v>7314451.908332602</v>
+        <v>7315195</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2002,24 +1827,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2046,37 +1856,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104432866</v>
+        <v>104432855</v>
       </c>
       <c r="B14" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2086,10 +1891,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553214.9228788411</v>
+        <v>553320</v>
       </c>
       <c r="R14" t="n">
-        <v>7314647.172137323</v>
+        <v>7314347</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2119,19 +1924,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,37 +1953,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104432863</v>
+        <v>104432869</v>
       </c>
       <c r="B15" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2198,10 +1988,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553257.1187990928</v>
+        <v>553324</v>
       </c>
       <c r="R15" t="n">
-        <v>7314400.599243836</v>
+        <v>7315224</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2231,19 +2021,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,12 +2053,7 @@
         <v>104432868</v>
       </c>
       <c r="B16" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2310,10 +2085,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553364.8332470444</v>
+        <v>553365</v>
       </c>
       <c r="R16" t="n">
-        <v>7314344.238168178</v>
+        <v>7314344</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2343,19 +2118,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,15 +2147,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104432874</v>
+        <v>104432863</v>
       </c>
       <c r="B17" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2398,21 +2158,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2422,10 +2182,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553428.2214174335</v>
+        <v>553257</v>
       </c>
       <c r="R17" t="n">
-        <v>7315192.746627835</v>
+        <v>7314400</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2455,19 +2215,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2494,37 +2244,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104796701</v>
+        <v>104432874</v>
       </c>
       <c r="B18" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1503</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2534,10 +2279,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553414.4696759391</v>
+        <v>553428</v>
       </c>
       <c r="R18" t="n">
-        <v>7315163.514466947</v>
+        <v>7315193</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2567,19 +2312,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,6 +2338,501 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>104432864</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tjulån södra, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>553379</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7315230</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>104432860</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tjulån södra, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>553207</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7314452</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>104432866</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tjulån södra, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>553215</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7314647</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>104432858</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tjulån södra, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>553223</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7314711</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>104432862</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tjulån södra, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>553439</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7315209</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10060-2022 artfynd.xlsx
+++ b/artfynd/A 10060-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104432856</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104432873</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104432872</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104432865</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796701</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104433019</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104432853</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104432876</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104432857</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1659,6 +1709,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70700986</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1756,6 +1811,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104432871</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1853,6 +1913,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104432867</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1950,6 +2015,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104432855</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2047,6 +2117,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104432869</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2144,6 +2219,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104432868</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2241,6 +2321,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104432863</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2338,6 +2423,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104432874</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2440,6 +2530,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104432864</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2542,6 +2637,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104432860</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2639,6 +2739,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104432866</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2736,6 +2841,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104432858</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2833,8 +2943,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104432862</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>